--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104635_W20.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104635_W20.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7596</v>
+        <v>5.0386</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4872</v>
+        <v>7.323</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.7276</v>
+        <v>-2.2844</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5948</v>
+        <v>2.59</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.1716</v>
+        <v>-1.1772</v>
       </c>
       <c r="I2" t="n">
-        <v>3.7664</v>
+        <v>3.7673</v>
       </c>
       <c r="J2" t="n">
-        <v>5.2213</v>
+        <v>5.1828</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6714</v>
+        <v>0.6475</v>
       </c>
       <c r="L2" t="n">
-        <v>4.5499</v>
+        <v>4.5352</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.6265</v>
+        <v>-2.5927</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.8429</v>
+        <v>-1.8248</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7835</v>
+        <v>-0.768</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8598</v>
+        <v>-0.5726</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2389</v>
+        <v>-0.3558</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6209</v>
+        <v>-0.2168</v>
       </c>
       <c r="V2" t="n">
-        <v>2.571</v>
+        <v>2.5659</v>
       </c>
       <c r="W2" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9587</v>
+        <v>0.3259</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3605</v>
+        <v>0.9863</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4018</v>
+        <v>-0.6604</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2092</v>
+        <v>3.2234</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4472</v>
+        <v>1.4502</v>
       </c>
       <c r="I3" t="n">
-        <v>1.762</v>
+        <v>1.7731</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5199</v>
+        <v>3.5068</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2512</v>
+        <v>2.2408</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2688</v>
+        <v>1.2661</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3107</v>
+        <v>-0.2835</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4932</v>
+        <v>0.5071</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.209</v>
+        <v>-0.8487</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1089</v>
+        <v>-0.2442</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3179</v>
+        <v>-0.6045</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.6405</v>
+        <v>-0.3632</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8646</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2241</v>
+        <v>0.1484</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1208</v>
+        <v>0.1397</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4071</v>
+        <v>-0.3969</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5278</v>
+        <v>0.5367</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1093</v>
+        <v>0.1089</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0115</v>
+        <v>0.0308</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4417</v>
+        <v>-0.4314</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2149</v>
+        <v>-0.9582000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9739</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2411</v>
+        <v>-0.3377</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. PUSTOVYI</t>
+          <t>K. KOSTADINOV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.6392</v>
+        <v>-1.5969</v>
       </c>
       <c r="E5" t="n">
-        <v>0.766</v>
+        <v>-1.6138</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.4052</v>
+        <v>0.0168</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3164</v>
+        <v>0.2732</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8803</v>
+        <v>-0.4137</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.1967</v>
+        <v>0.6869</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7133</v>
+        <v>-0.3299</v>
       </c>
       <c r="K5" t="n">
-        <v>1.967</v>
+        <v>0.348</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7463</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.0298</v>
+        <v>0.6032</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0867</v>
+        <v>-0.7617</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.9431</v>
+        <v>1.3648</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.8147</v>
+        <v>0.4553</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.4952</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3312</v>
+        <v>-0.849</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3871</v>
+        <v>-0.6692</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.056</v>
+        <v>-0.1797</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1607</v>
+        <v>-1.4764</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>-0.387</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. ORTEGA</t>
+          <t>A. PUSTOVYI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.1019</v>
+        <v>-2.155</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2643</v>
+        <v>0.3842</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.3662</v>
+        <v>-2.5392</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6131</v>
+        <v>-0.3117</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6291</v>
+        <v>0.8735000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.016</v>
+        <v>-1.1852</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0352</v>
+        <v>2.6958</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8658</v>
+        <v>1.951</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.901</v>
+        <v>0.7447</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6483</v>
+        <v>-3.0075</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2368</v>
+        <v>-1.0775</v>
       </c>
       <c r="O6" t="n">
-        <v>0.885</v>
+        <v>-1.93</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4537</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1155</v>
+        <v>-0.18</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2994</v>
+        <v>0.0346</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.415</v>
+        <v>-0.2146</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.0531</v>
+        <v>0.1578</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.0531</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. KOSTADINOV</t>
+          <t>C. ORTEGA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1215</v>
+        <v>-2.2605</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8346</v>
+        <v>0.0177</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2869</v>
+        <v>-2.2781</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2668</v>
+        <v>0.6138</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4156</v>
+        <v>0.6317</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6824</v>
+        <v>-0.018</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3179</v>
+        <v>-0.0472</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3565</v>
+        <v>0.8618</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6744</v>
+        <v>-0.909</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5847</v>
+        <v>0.6609</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7721</v>
+        <v>-0.2301</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3568</v>
+        <v>0.8911</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3637</v>
+        <v>-0.2903</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9043</v>
+        <v>0.0648</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4594</v>
+        <v>-0.3551</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4783</v>
+        <v>-3.0392</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3856</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>-3.0392</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Y. PONS</t>
+          <t>M. UDEZE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.161</v>
+        <v>-3.2784</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3506</v>
+        <v>-2.9637</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.8104</v>
+        <v>-0.3147</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9151</v>
+        <v>-2.0769</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9337</v>
+        <v>-2.0191</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0186</v>
+        <v>-0.0578</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6001</v>
+        <v>-1.3469</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1456</v>
+        <v>-1.4586</v>
       </c>
       <c r="L8" t="n">
-        <v>1.7458</v>
+        <v>0.1117</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.5152</v>
+        <v>-0.73</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.788</v>
+        <v>-0.5604</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.7272</v>
+        <v>-0.1695</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.0415</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2683</v>
+        <v>-1.3658</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2044</v>
+        <v>0.0245</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3176</v>
+        <v>-0.251</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.522</v>
+        <v>0.2755</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. UDEZE</t>
+          <t>Y. PONS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3032</v>
+        <v>-3.3367</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1875</v>
+        <v>-0.7362</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1158</v>
+        <v>-2.6006</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.0826</v>
+        <v>-0.9164</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.0187</v>
+        <v>-0.928</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0639</v>
+        <v>0.0116</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3395</v>
+        <v>1.5752</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.4515</v>
+        <v>-0.1519</v>
       </c>
       <c r="L9" t="n">
-        <v>0.112</v>
+        <v>1.7271</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7431</v>
+        <v>-2.4916</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5672</v>
+        <v>-0.7761</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1759</v>
+        <v>-1.7155</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9073</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.361</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="S9" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.3717</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4869</v>
+        <v>-0.0351</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4951</v>
+        <v>-0.3366</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7136</v>
+        <v>-3.6758</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9263</v>
+        <v>-2.5895</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7874</v>
+        <v>-1.0863</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.7519</v>
+        <v>-2.7514</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2915</v>
+        <v>-0.2874</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.4603</v>
+        <v>-2.464</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0784</v>
+        <v>-1.0912</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0866</v>
+        <v>0.0862</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1649</v>
+        <v>-1.1773</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6735</v>
+        <v>-1.6603</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3781</v>
+        <v>-0.3736</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2954</v>
+        <v>-1.2866</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2813</v>
+        <v>-0.2415</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4869</v>
+        <v>-0.1326</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2056</v>
+        <v>-0.1089</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.1512</v>
+        <v>-5.524</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5229</v>
+        <v>-4.8017</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6283</v>
+        <v>-0.7224</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.4667</v>
+        <v>-3.4673</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.668</v>
+        <v>-0.6746</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.7988</v>
+        <v>-2.7928</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.0206</v>
+        <v>-2.0523</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1519</v>
+        <v>0.1304</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.1725</v>
+        <v>-2.1827</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4461</v>
+        <v>-1.415</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8198</v>
+        <v>-0.805</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6263</v>
+        <v>-0.61</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.643</v>
+        <v>-1.008</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3266</v>
+        <v>-0.5625</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3164</v>
+        <v>-0.4455</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. BEST</t>
+          <t>S. EVANS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.6355</v>
+        <v>-7.9909</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9091</v>
+        <v>-4.8397</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.7264</v>
+        <v>-3.1513</v>
       </c>
       <c r="G12" t="n">
-        <v>-7.4306</v>
+        <v>-5.0965</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.2005</v>
+        <v>-3.6957</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.2301</v>
+        <v>-1.4008</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.3323</v>
+        <v>-1.5154</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.9088</v>
+        <v>-2.259</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4234</v>
+        <v>0.7436</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.0983</v>
+        <v>-3.5811</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.2917</v>
+        <v>-1.4367</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.8066</v>
+        <v>-2.1444</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4537</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.361</v>
+        <v>-2.7316</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7513</v>
+        <v>-0.4392</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3085</v>
+        <v>-0.5927</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4428</v>
+        <v>0.1535</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. EVANS</t>
+          <t>A. BEST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.6797</v>
+        <v>-8.618600000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.3692</v>
+        <v>-4.0529</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.3105</v>
+        <v>-4.5657</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.0725</v>
+        <v>-7.4176</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.6837</v>
+        <v>-3.1995</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.3888</v>
+        <v>-4.2181</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.4646</v>
+        <v>-3.3511</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.2347</v>
+        <v>-1.9208</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7701</v>
+        <v>-1.4303</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.6079</v>
+        <v>-4.0665</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.4489</v>
+        <v>-1.2788</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.159</v>
+        <v>-2.7877</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.361</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.722</v>
+        <v>-1.3658</v>
       </c>
       <c r="R13" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1535</v>
+        <v>-0.7458</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1825</v>
+        <v>-0.4255</v>
       </c>
       <c r="U13" t="n">
-        <v>0.029</v>
+        <v>-0.3202</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-33.429</v>
+        <v>-33.4355</v>
       </c>
       <c r="E14" t="n">
-        <v>-13.0868</v>
+        <v>-13.3979</v>
       </c>
       <c r="F14" t="n">
-        <v>-20.3424</v>
+        <v>-20.0379</v>
       </c>
       <c r="G14" t="n">
-        <v>-15.2311</v>
+        <v>-15.1977</v>
       </c>
       <c r="H14" t="n">
-        <v>-9.8338</v>
+        <v>-9.8367</v>
       </c>
       <c r="I14" t="n">
-        <v>-5.3974</v>
+        <v>-5.3611</v>
       </c>
       <c r="J14" t="n">
-        <v>3.575399999999999</v>
+        <v>3.335500000000002</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6444000000000001</v>
+        <v>0.5099000000000002</v>
       </c>
       <c r="L14" t="n">
-        <v>2.931299999999999</v>
+        <v>2.8257</v>
       </c>
       <c r="M14" t="n">
-        <v>-18.8066</v>
+        <v>-18.5333</v>
       </c>
       <c r="N14" t="n">
-        <v>-10.4778</v>
+        <v>-10.3467</v>
       </c>
       <c r="O14" t="n">
-        <v>-8.328800000000001</v>
+        <v>-8.186499999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>-9.073200000000002</v>
+        <v>-9.1052</v>
       </c>
       <c r="Q14" t="n">
-        <v>-17.0124</v>
+        <v>-17.0723</v>
       </c>
       <c r="R14" t="n">
-        <v>7.9392</v>
+        <v>7.9672</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.457</v>
+        <v>-6.480499999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.7955</v>
+        <v>-3.7897</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.6618</v>
+        <v>-2.6906</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.6675</v>
+        <v>-2.6522</v>
       </c>
       <c r="W14" t="n">
-        <v>4.145799999999999</v>
+        <v>4.1287</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.8133</v>
+        <v>-6.781000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.948600000000001</v>
+        <v>8.743600000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>6.5948</v>
+        <v>6.3189</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3538</v>
+        <v>2.4247</v>
       </c>
       <c r="G15" t="n">
-        <v>4.4326</v>
+        <v>4.4243</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0981</v>
+        <v>1.0999</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3345</v>
+        <v>3.3244</v>
       </c>
       <c r="J15" t="n">
-        <v>5.4628</v>
+        <v>5.4249</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7765</v>
+        <v>1.7614</v>
       </c>
       <c r="L15" t="n">
-        <v>3.6862</v>
+        <v>3.6634</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0302</v>
+        <v>-1.0006</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6785</v>
+        <v>-0.6615</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3517</v>
+        <v>-0.3391</v>
       </c>
       <c r="P15" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4745</v>
+        <v>0.2706</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0393</v>
+        <v>-0.1955</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4352</v>
+        <v>0.4661</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.7367</v>
+        <v>6.7454</v>
       </c>
       <c r="E16" t="n">
-        <v>6.5081</v>
+        <v>6.1173</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2286</v>
+        <v>0.6282</v>
       </c>
       <c r="G16" t="n">
-        <v>6.9434</v>
+        <v>6.9267</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5036</v>
+        <v>0.5027</v>
       </c>
       <c r="I16" t="n">
-        <v>6.4398</v>
+        <v>6.424</v>
       </c>
       <c r="J16" t="n">
-        <v>7.2733</v>
+        <v>7.2394</v>
       </c>
       <c r="K16" t="n">
-        <v>0.599</v>
+        <v>0.5893</v>
       </c>
       <c r="L16" t="n">
-        <v>6.6743</v>
+        <v>6.6501</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3299</v>
+        <v>-0.3127</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.114</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>0.369</v>
+        <v>0.0161</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.483</v>
+        <v>-0.1078</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="17">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.6811</v>
+        <v>5.6151</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8816</v>
+        <v>2.9723</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7995</v>
+        <v>2.6428</v>
       </c>
       <c r="G17" t="n">
-        <v>4.4203</v>
+        <v>4.4279</v>
       </c>
       <c r="H17" t="n">
-        <v>2.541</v>
+        <v>2.5418</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8793</v>
+        <v>1.8862</v>
       </c>
       <c r="J17" t="n">
-        <v>4.526</v>
+        <v>4.5101</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5109</v>
+        <v>2.4993</v>
       </c>
       <c r="L17" t="n">
-        <v>2.0151</v>
+        <v>2.0108</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1057</v>
+        <v>-0.0822</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0301</v>
+        <v>0.0424</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1359</v>
+        <v>-0.1246</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1681</v>
+        <v>0.0977</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4688</v>
+        <v>-0.351</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6369</v>
+        <v>0.4487</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.776</v>
+        <v>3.9466</v>
       </c>
       <c r="E18" t="n">
-        <v>2.608</v>
+        <v>3.0588</v>
       </c>
       <c r="F18" t="n">
-        <v>1.168</v>
+        <v>0.8878</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9941</v>
+        <v>3.3929</v>
       </c>
       <c r="H18" t="n">
-        <v>0.922</v>
+        <v>3.3929</v>
       </c>
       <c r="I18" t="n">
-        <v>0.07199999999999999</v>
+        <v>-0</v>
       </c>
       <c r="J18" t="n">
-        <v>2.118</v>
+        <v>3.633</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2224</v>
+        <v>3.3505</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8956</v>
+        <v>0.2826</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1239</v>
+        <v>-0.2402</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3003</v>
+        <v>0.0424</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8236</v>
+        <v>-0.2826</v>
       </c>
       <c r="P18" t="n">
-        <v>2.0415</v>
+        <v>0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0415</v>
+        <v>1.5934</v>
       </c>
       <c r="S18" t="n">
-        <v>1.126</v>
+        <v>1.188</v>
       </c>
       <c r="T18" t="n">
-        <v>1.2612</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1352</v>
+        <v>0.624</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3856</v>
+        <v>-1.0895</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3856</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.3332</v>
+        <v>3.1859</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5086</v>
+        <v>1.7683</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8246</v>
+        <v>1.4177</v>
       </c>
       <c r="G19" t="n">
-        <v>3.41</v>
+        <v>1.0028</v>
       </c>
       <c r="H19" t="n">
-        <v>3.41</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.0808</v>
       </c>
       <c r="J19" t="n">
-        <v>3.673</v>
+        <v>2.1035</v>
       </c>
       <c r="K19" t="n">
-        <v>3.3799</v>
+        <v>1.2098</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2931</v>
+        <v>0.8937</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.263</v>
+        <v>-1.1007</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0301</v>
+        <v>-0.2879</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2931</v>
+        <v>-0.8129</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4537</v>
+        <v>2.0487</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5878</v>
+        <v>2.0487</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5622</v>
+        <v>0.5214</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0302</v>
+        <v>0.4387</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5925</v>
+        <v>0.0827</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0927</v>
+        <v>-0.387</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0927</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.3727</v>
+        <v>2.5164</v>
       </c>
       <c r="E20" t="n">
-        <v>1.971</v>
+        <v>1.8369</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4018</v>
+        <v>0.6795</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6713</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6393</v>
+        <v>0.635</v>
       </c>
       <c r="I20" t="n">
-        <v>0.032</v>
+        <v>0.0359</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9184</v>
+        <v>0.8966</v>
       </c>
       <c r="K20" t="n">
-        <v>0.436</v>
+        <v>0.4202</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4824</v>
+        <v>0.4764</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2471</v>
+        <v>-0.2257</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1817</v>
+        <v>1.3203</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0525</v>
+        <v>0.9403</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1291</v>
+        <v>0.3801</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.5449</v>
+        <v>1.8269</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8992</v>
+        <v>0.9944</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.8326</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.114</v>
+        <v>-1.1137</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4054</v>
+        <v>0.4104</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5194</v>
+        <v>-1.5241</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3901</v>
+        <v>-0.4129</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7375</v>
+        <v>0.7272</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.1276</v>
+        <v>-1.1401</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7239</v>
+        <v>-0.7007</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3321</v>
+        <v>-0.3168</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.8024</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1966</v>
+        <v>0.3178</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3281</v>
+        <v>0.4846</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="22">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.5084</v>
+        <v>1.5605</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2019</v>
+        <v>-0.1116</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7103</v>
+        <v>1.6721</v>
       </c>
       <c r="G22" t="n">
-        <v>1.0466</v>
+        <v>1.0413</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4647</v>
+        <v>-0.4598</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5113</v>
+        <v>1.5011</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1923</v>
+        <v>1.1684</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1803</v>
+        <v>-0.1864</v>
       </c>
       <c r="L22" t="n">
-        <v>1.3726</v>
+        <v>1.3548</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1458</v>
+        <v>-0.1271</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.064</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2601</v>
+        <v>-0.1418</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2683</v>
+        <v>0.2058</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Y. SIMA</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8864</v>
+        <v>1.0652</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3316</v>
+        <v>-0.1036</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2179</v>
+        <v>1.1688</v>
       </c>
       <c r="G23" t="n">
-        <v>0.192</v>
+        <v>-1.4654</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2265</v>
+        <v>1.249</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4185</v>
+        <v>-2.7144</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.3149</v>
+        <v>-1.7988</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.163</v>
+        <v>0.6895</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.152</v>
+        <v>-2.4883</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5069</v>
+        <v>0.3335</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0636</v>
+        <v>0.5595</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5705</v>
+        <v>-0.226</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3995</v>
+        <v>0.8768</v>
       </c>
       <c r="T23" t="n">
-        <v>0.369</v>
+        <v>0.4967</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0305</v>
+        <v>0.3801</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3856</v>
+        <v>2.3367</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3856</v>
+        <v>2.3367</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>Y. SIMA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0688</v>
+        <v>0.9347</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7978</v>
+        <v>-0.5782</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7289</v>
+        <v>1.5129</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7223000000000001</v>
+        <v>0.1917</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8585</v>
+        <v>-0.2269</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.5807</v>
+        <v>0.4186</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4669</v>
+        <v>-0.3257</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6234</v>
+        <v>-0.1691</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.0903</v>
+        <v>-0.1566</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2554</v>
+        <v>0.5174</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2351</v>
+        <v>-0.0578</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4904</v>
+        <v>0.5752</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>1.0425</v>
+        <v>0.4471</v>
       </c>
       <c r="T24" t="n">
-        <v>1.1039</v>
+        <v>0.1345</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0614</v>
+        <v>0.3126</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.387</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1607</v>
+        <v>-0.387</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1219</v>
+        <v>-0.2658</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.0198</v>
+        <v>0.1931</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8979</v>
+        <v>-0.4588</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.4659</v>
+        <v>-0.7241</v>
       </c>
       <c r="H25" t="n">
-        <v>1.2423</v>
+        <v>0.8642</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.7082</v>
+        <v>-1.5883</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.7811</v>
+        <v>-0.4823</v>
       </c>
       <c r="K25" t="n">
-        <v>0.6927</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.4737</v>
+        <v>-1.1029</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3151</v>
+        <v>-0.2417</v>
       </c>
       <c r="N25" t="n">
-        <v>0.5496</v>
+        <v>0.2437</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.2345</v>
+        <v>-0.4854</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3215</v>
+        <v>0.7071</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4506</v>
+        <v>0.5177</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1291</v>
+        <v>0.1895</v>
       </c>
       <c r="V25" t="n">
-        <v>2.3461</v>
+        <v>-0.9317</v>
       </c>
       <c r="W25" t="n">
-        <v>2.3461</v>
+        <v>0.1578</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.3059</v>
+        <v>-1.6495</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.8733</v>
+        <v>-2.4288</v>
       </c>
       <c r="F26" t="n">
-        <v>1.5674</v>
+        <v>0.7793</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.5768</v>
+        <v>-3.5776</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.0952</v>
+        <v>-1.0943</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.4816</v>
+        <v>-2.4833</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.4042</v>
+        <v>-3.4228</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.1571</v>
+        <v>-1.1656</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.2471</v>
+        <v>-2.2572</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1726</v>
+        <v>-0.1548</v>
       </c>
       <c r="N26" t="n">
-        <v>0.0619</v>
+        <v>0.0713</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R26" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S26" t="n">
-        <v>1.4051</v>
+        <v>1.0663</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5202</v>
+        <v>-0.0468</v>
       </c>
       <c r="U26" t="n">
-        <v>1.9253</v>
+        <v>1.1131</v>
       </c>
       <c r="V26" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W26" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>33.42900000000001</v>
+        <v>34.22499999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>20.3425</v>
+        <v>20.0378</v>
       </c>
       <c r="F27" t="n">
-        <v>13.0866</v>
+        <v>14.1876</v>
       </c>
       <c r="G27" t="n">
-        <v>15.2313</v>
+        <v>15.1977</v>
       </c>
       <c r="H27" t="n">
-        <v>9.8338</v>
+        <v>9.8368</v>
       </c>
       <c r="I27" t="n">
-        <v>5.397499999999999</v>
+        <v>5.360900000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>18.8066</v>
+        <v>18.5334</v>
       </c>
       <c r="K27" t="n">
-        <v>10.4779</v>
+        <v>10.3466</v>
       </c>
       <c r="L27" t="n">
-        <v>8.328600000000002</v>
+        <v>8.186700000000002</v>
       </c>
       <c r="M27" t="n">
-        <v>-3.575499999999999</v>
+        <v>-3.3355</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.6442000000000001</v>
+        <v>-0.5098999999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>-2.9312</v>
+        <v>-2.8256</v>
       </c>
       <c r="P27" t="n">
-        <v>9.073399999999999</v>
+        <v>9.105399999999999</v>
       </c>
       <c r="Q27" t="n">
-        <v>-7.939299999999999</v>
+        <v>-7.967300000000002</v>
       </c>
       <c r="R27" t="n">
-        <v>17.0123</v>
+        <v>17.0723</v>
       </c>
       <c r="S27" t="n">
-        <v>6.457</v>
+        <v>7.2699</v>
       </c>
       <c r="T27" t="n">
-        <v>2.6616</v>
+        <v>2.6907</v>
       </c>
       <c r="U27" t="n">
-        <v>3.7954</v>
+        <v>4.5795</v>
       </c>
       <c r="V27" t="n">
-        <v>2.6676</v>
+        <v>2.6522</v>
       </c>
       <c r="W27" t="n">
-        <v>6.8134</v>
+        <v>6.781000000000001</v>
       </c>
       <c r="X27" t="n">
-        <v>-4.1458</v>
+        <v>-4.128699999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104635_W20.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104635_W20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104635_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104635_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104635_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104635_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104635_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-3.0392</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104635_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104635_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104635_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104635_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104635_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104635_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104635_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-6.781000000000001</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104635_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104635_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104635_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104635_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104635_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104635_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104635_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104635_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104635_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104635_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104635_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104635_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-4.128699999999999</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
